--- a/Docs/Requirments/RTM.xlsx
+++ b/Docs/Requirments/RTM.xlsx
@@ -1,31 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30002"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA-Project\QA-project-tool\Docs\Requirments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/10F4B66B2306BB74/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB94A668-6466-4528-98D7-61F275F854E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05004D6B-63CC-44BA-8DDA-71E36D81B688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="RTM" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="250">
+  <si>
+    <t>Feature</t>
+  </si>
   <si>
     <t>CRS</t>
   </si>
@@ -33,14 +47,841 @@
     <t>SRS</t>
   </si>
   <si>
-    <t>Feature</t>
+    <t>Do</t>
+  </si>
+  <si>
+    <t>ToDo</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>REQ-01</t>
+  </si>
+  <si>
+    <t>UL-01</t>
+  </si>
+  <si>
+    <t>TC_UserLogin_007</t>
+  </si>
+  <si>
+    <t>UL-02</t>
+  </si>
+  <si>
+    <t>TC_UserLogin_010</t>
+  </si>
+  <si>
+    <t>UL-03</t>
+  </si>
+  <si>
+    <t>TC_UserLogin_004</t>
+  </si>
+  <si>
+    <t>UL-04</t>
+  </si>
+  <si>
+    <t>TC_UserLogin_008</t>
+  </si>
+  <si>
+    <t>UL-05</t>
+  </si>
+  <si>
+    <t>TC_UserLogin_006 ,
+ TC_UserLogin_009</t>
+  </si>
+  <si>
+    <t>UL-06</t>
+  </si>
+  <si>
+    <t>TC_UserLogin_005</t>
+  </si>
+  <si>
+    <t>UL-07</t>
+  </si>
+  <si>
+    <t>TC_UserLogin_003</t>
+  </si>
+  <si>
+    <t>UL-08</t>
+  </si>
+  <si>
+    <t>UL-09</t>
+  </si>
+  <si>
+    <t>TC_UserLogin_001</t>
+  </si>
+  <si>
+    <t>UL-10</t>
+  </si>
+  <si>
+    <t>TC_UserLogin_011</t>
+  </si>
+  <si>
+    <t>UL-11</t>
+  </si>
+  <si>
+    <t>TC_UserLogin_002</t>
+  </si>
+  <si>
+    <t>Register</t>
+  </si>
+  <si>
+    <t>REQ-02</t>
+  </si>
+  <si>
+    <t>UR-01</t>
+  </si>
+  <si>
+    <t>TC_Registration_001,
+TC_Registration_002</t>
+  </si>
+  <si>
+    <t>UR-02</t>
+  </si>
+  <si>
+    <t>TC_Registration_001,
+TC_Registration_003</t>
+  </si>
+  <si>
+    <t>UR-03</t>
+  </si>
+  <si>
+    <t>TC_Registration_001,
+TC_Registration_004,
+TC_Registration_005,
+TC_Registration_006,
+TC_Registration_007</t>
+  </si>
+  <si>
+    <t>UR-04</t>
+  </si>
+  <si>
+    <t>TC_Registration_008,
+TC_Registration_009</t>
+  </si>
+  <si>
+    <t>UR-05</t>
+  </si>
+  <si>
+    <t>TC_Registration_010,
+TC_Registration_011,
+TC_Registration_012</t>
+  </si>
+  <si>
+    <t>UR-06</t>
+  </si>
+  <si>
+    <t>TC_Registration_001,
+TC_Registration_013,
+TC_Registration_014</t>
+  </si>
+  <si>
+    <t>UR-07</t>
+  </si>
+  <si>
+    <t>TC_Registration_001,
+TC_Registration_015,
+TC_Registration_017,
+TC_Registration_018</t>
+  </si>
+  <si>
+    <t>UR-08</t>
+  </si>
+  <si>
+    <t>TC_Registration_016</t>
+  </si>
+  <si>
+    <t>UR-09</t>
+  </si>
+  <si>
+    <t>TC_Registration_001,
+TC_Registration_019</t>
+  </si>
+  <si>
+    <t>UR-10</t>
+  </si>
+  <si>
+    <t>TC_Registration_001,
+TC_Registration_020</t>
+  </si>
+  <si>
+    <t>UR-11</t>
+  </si>
+  <si>
+    <t>TC_Registration_001,
+TC_Registration_021,
+TC_Registration_022,
+TC_Registration_023,
+TC_Registration_024</t>
+  </si>
+  <si>
+    <t>UR-12</t>
+  </si>
+  <si>
+    <t>TC_Registration_001,
+TC_Registration_025</t>
+  </si>
+  <si>
+    <t>UR-13</t>
+  </si>
+  <si>
+    <t>TC_Registration_001,
+TC_Registration_026</t>
+  </si>
+  <si>
+    <t>UR-14</t>
+  </si>
+  <si>
+    <t>TC_Registration_002,
+TC_Registration_003,
+TC_Registration_004,
+TC_Registration_005,
+TC_Registration_006,
+TC_Registration_007,
+TC_Registration_008,
+TC_Registration_009,
+TC_Registration_013,
+TC_Registration_014,
+TC_Registration_015,
+TC_Registration_016,
+TC_Registration_017,
+TC_Registration_018,
+TC_Registration_019,
+TC_Registration_020,
+TC_Registration_021,
+TC_Registration_022,
+TC_Registration_023,
+TC_Registration_024,
+TC_Registration_025,
+TC_Registration_026,
+TC_Registration_027</t>
+  </si>
+  <si>
+    <t>UR-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_Registration_001 </t>
+  </si>
+  <si>
+    <t>UR-16</t>
+  </si>
+  <si>
+    <t>UR-17</t>
+  </si>
+  <si>
+    <t>TC_Registration_028</t>
+  </si>
+  <si>
+    <t>Home Page</t>
+  </si>
+  <si>
+    <t>REQ_03</t>
+  </si>
+  <si>
+    <t>HP-01</t>
+  </si>
+  <si>
+    <t>TC_HomePage_001</t>
+  </si>
+  <si>
+    <t>HP-02</t>
+  </si>
+  <si>
+    <t>TC_HomePage_002</t>
+  </si>
+  <si>
+    <t>HP-03</t>
+  </si>
+  <si>
+    <t>TC_HomePage_003</t>
+  </si>
+  <si>
+    <t>HP-04</t>
+  </si>
+  <si>
+    <t>HP-05</t>
+  </si>
+  <si>
+    <t>HP-06</t>
+  </si>
+  <si>
+    <t>HP-07</t>
+  </si>
+  <si>
+    <t>HP-08</t>
+  </si>
+  <si>
+    <t>HP-09</t>
+  </si>
+  <si>
+    <t>HP-10</t>
+  </si>
+  <si>
+    <t>HP-11</t>
+  </si>
+  <si>
+    <t>TC_HomePage_013</t>
+  </si>
+  <si>
+    <t>HP-12</t>
+  </si>
+  <si>
+    <t>TC_HomePage_014</t>
+  </si>
+  <si>
+    <t>HP-13</t>
+  </si>
+  <si>
+    <t>TC_HomePage_015</t>
+  </si>
+  <si>
+    <t>HP-14</t>
+  </si>
+  <si>
+    <t>TC_HomePage_016</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Gallery</t>
+    </r>
+  </si>
+  <si>
+    <t>REQ_4</t>
+  </si>
+  <si>
+    <t>GP-01</t>
+  </si>
+  <si>
+    <t>TC_GallaryPage_001</t>
+  </si>
+  <si>
+    <t>Destination Details</t>
+  </si>
+  <si>
+    <t>REQ_6</t>
+  </si>
+  <si>
+    <t>DD-01</t>
+  </si>
+  <si>
+    <t>TC_DestinationDetails_001,
+TC_DestinationDetails_002</t>
+  </si>
+  <si>
+    <t>DD-02</t>
+  </si>
+  <si>
+    <t>TC_DestinationDetails_003,
+TC_DestinationDetails_004</t>
+  </si>
+  <si>
+    <t>DD-03</t>
+  </si>
+  <si>
+    <t>TC_DestinationDetails_005</t>
+  </si>
+  <si>
+    <t>Flight Search</t>
+  </si>
+  <si>
+    <t>REQ_7</t>
+  </si>
+  <si>
+    <t>FS-01</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_001,
+TC_FlightSearch_002,
+TC_FlightSearch_003</t>
+  </si>
+  <si>
+    <t>FS-02</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_001,
+TC_FlightSearch_004,
+TC_FlightSearch_005</t>
+  </si>
+  <si>
+    <t>FS-03</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_006</t>
+  </si>
+  <si>
+    <t>FS-04</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_007</t>
+  </si>
+  <si>
+    <t>FS-05</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_008</t>
+  </si>
+  <si>
+    <t>FS-06</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_009</t>
+  </si>
+  <si>
+    <t>FS-07</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_001,
+TC_FlightSearch_010</t>
+  </si>
+  <si>
+    <t>FS-08</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_011,
+TC_FlightSearch_013</t>
+  </si>
+  <si>
+    <t>FS-09</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_012,
+TC_FlightSearch_013</t>
+  </si>
+  <si>
+    <t>FS-10</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_001,
+TC_FlightSearch_014,
+TC_FlightSearch_015</t>
+  </si>
+  <si>
+    <t>FS-11</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_016,
+TC_FlightSearch_017,
+TC_FlightSearch_018</t>
+  </si>
+  <si>
+    <t>FS-12</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_019,
+TC_FlightSearch_020</t>
+  </si>
+  <si>
+    <t>FS-13</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_021,
+TC_FlightSearch_022,
+TC_FlightSearch_023,
+TC_FlightSearch_024</t>
+  </si>
+  <si>
+    <t>FS-14</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_025,
+TC_FlightSearch_026,
+TC_FlightSearch_027</t>
+  </si>
+  <si>
+    <t>FS-15</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_028</t>
+  </si>
+  <si>
+    <t>FS-16</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_029</t>
+  </si>
+  <si>
+    <t>FS-17</t>
+  </si>
+  <si>
+    <t>TC_FlightSearch_030,
+TC_FlightSearch_031</t>
+  </si>
+  <si>
+    <t>Not Done Yet</t>
+  </si>
+  <si>
+    <t>Flight Result</t>
+  </si>
+  <si>
+    <t>FRS-01</t>
+  </si>
+  <si>
+    <t>FRS-02</t>
+  </si>
+  <si>
+    <t>FRS-03</t>
+  </si>
+  <si>
+    <t>FRS-04</t>
+  </si>
+  <si>
+    <t>FRS-05</t>
+  </si>
+  <si>
+    <t>FRS-06</t>
+  </si>
+  <si>
+    <t>Passenger Details</t>
+  </si>
+  <si>
+    <t>REQ_9</t>
+  </si>
+  <si>
+    <t>PD-01</t>
+  </si>
+  <si>
+    <t>PD-02</t>
+  </si>
+  <si>
+    <t>PD-03</t>
+  </si>
+  <si>
+    <t>PD-04</t>
+  </si>
+  <si>
+    <t>PD-05</t>
+  </si>
+  <si>
+    <t>PD-06</t>
+  </si>
+  <si>
+    <t>PD-07</t>
+  </si>
+  <si>
+    <t>PD-08</t>
+  </si>
+  <si>
+    <t>PD-09</t>
+  </si>
+  <si>
+    <t>PD-10</t>
+  </si>
+  <si>
+    <t>PD-11</t>
+  </si>
+  <si>
+    <t>PD-12</t>
+  </si>
+  <si>
+    <t>PD-13</t>
+  </si>
+  <si>
+    <t>PD-14</t>
+  </si>
+  <si>
+    <t>PD-15</t>
+  </si>
+  <si>
+    <t>PD-16</t>
+  </si>
+  <si>
+    <t>PD-17</t>
+  </si>
+  <si>
+    <t>PD-18</t>
+  </si>
+  <si>
+    <t>PD-19</t>
+  </si>
+  <si>
+    <t>Not Done Yet(Ahmed Nabil)</t>
+  </si>
+  <si>
+    <t>Admin Login</t>
+  </si>
+  <si>
+    <t>REQ_11</t>
+  </si>
+  <si>
+    <t>AL-01</t>
+  </si>
+  <si>
+    <t>AL-02</t>
+  </si>
+  <si>
+    <t>AL-03</t>
+  </si>
+  <si>
+    <t>AL-04</t>
+  </si>
+  <si>
+    <t>AL-05</t>
+  </si>
+  <si>
+    <t>AL-06</t>
+  </si>
+  <si>
+    <t>AL-07</t>
+  </si>
+  <si>
+    <t>AL-08</t>
+  </si>
+  <si>
+    <t>AL-09</t>
+  </si>
+  <si>
+    <t>AL-10</t>
+  </si>
+  <si>
+    <t>AL-11</t>
+  </si>
+  <si>
+    <t>Admin Dashboard</t>
+  </si>
+  <si>
+    <t>REQ_12</t>
+  </si>
+  <si>
+    <t>AD-01</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_001</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_002</t>
+  </si>
+  <si>
+    <t>AD-02</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_003</t>
+  </si>
+  <si>
+    <t>AD-03</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_004</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_005</t>
+  </si>
+  <si>
+    <t>AD-04</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_006</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_007</t>
+  </si>
+  <si>
+    <t>AD-05</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_008</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_009</t>
+  </si>
+  <si>
+    <t>AD-06</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_010</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_011</t>
+  </si>
+  <si>
+    <t>AD-07</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_012</t>
+  </si>
+  <si>
+    <t>AD-08</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_013</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_014</t>
+  </si>
+  <si>
+    <t>AD-09</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_015</t>
+  </si>
+  <si>
+    <t>AD-10</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_016</t>
+  </si>
+  <si>
+    <t>AD-11</t>
+  </si>
+  <si>
+    <t>TC_AdminDashboard_017</t>
+  </si>
+  <si>
+    <t>Customer Management</t>
+  </si>
+  <si>
+    <t>REQ_13</t>
+  </si>
+  <si>
+    <t>CM-01</t>
+  </si>
+  <si>
+    <t>TC_CustomerManagement_001</t>
+  </si>
+  <si>
+    <t>CM-02</t>
+  </si>
+  <si>
+    <t>TC_CustomerManagement_002</t>
+  </si>
+  <si>
+    <t>CM-03</t>
+  </si>
+  <si>
+    <t>TC_CustomerManagement_003</t>
+  </si>
+  <si>
+    <t>Zahran Will do it</t>
+  </si>
+  <si>
+    <t>Edit Customer</t>
+  </si>
+  <si>
+    <t>REQ_14</t>
+  </si>
+  <si>
+    <t>EC-01</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_001</t>
+  </si>
+  <si>
+    <t>EC-02</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_008
+TC_EditCustomer_009</t>
+  </si>
+  <si>
+    <t>EC-03</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_018
+TC_EditCustomer_019</t>
+  </si>
+  <si>
+    <t>EC-04</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_006</t>
+  </si>
+  <si>
+    <t>EC-05</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_010
+TC_EditCustomer_011
+TC_EditCustomer_012</t>
+  </si>
+  <si>
+    <t>EC-06</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_007</t>
+  </si>
+  <si>
+    <t>EC-07</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_005 
+TC_EditCustomer_013</t>
+  </si>
+  <si>
+    <t>EC-08</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_014
+TC_EditCustomer_015
+TC_EditCustomer_016
+TC_EditCustomer_017</t>
+  </si>
+  <si>
+    <t>EC-09</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_003</t>
+  </si>
+  <si>
+    <t>EC-10</t>
+  </si>
+  <si>
+    <t>EC-11</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_002
+TC_EditCustomer_003</t>
+  </si>
+  <si>
+    <t>EC-12</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_002
+TC_EditCustomer_020</t>
+  </si>
+  <si>
+    <t>EC-13</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_003
+TC_EditCustomer_020
+TC_EditCustomer_022</t>
+  </si>
+  <si>
+    <t>EC-14</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_021</t>
+  </si>
+  <si>
+    <t>EC-15</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_023</t>
+  </si>
+  <si>
+    <t>EC-16</t>
+  </si>
+  <si>
+    <t>TC_EditCustomer_004</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -55,8 +896,80 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -69,8 +982,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -78,13 +997,134 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -365,26 +1405,1561 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G165"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.109375" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="21">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="27"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="27"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="26.25">
+      <c r="A6" s="27"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="27"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="27"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="27"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="27"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="27"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="27"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="2" customFormat="1"/>
+    <row r="14" spans="1:6" ht="26.25">
+      <c r="A14" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="26.25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="64.5">
+      <c r="A16" s="25"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="26.25">
+      <c r="A17" s="25"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="39">
+      <c r="A18" s="25"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="39">
+      <c r="A19" s="25"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="51.75">
+      <c r="A20" s="25"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="25"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="26.25">
+      <c r="A22" s="25"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="26.25">
+      <c r="A23" s="29"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="64.5">
+      <c r="A24" s="29"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="26.25">
+      <c r="A25" s="29"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="26.25">
+      <c r="A26" s="29"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="294">
+      <c r="A27" s="29"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="29"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="29"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="29"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="3" customFormat="1" ht="15.75">
+      <c r="A31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="25"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="25"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="25"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="25"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="25"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="25"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="25"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="25"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="25"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="25"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="25"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="25"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="25"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="3" customFormat="1"/>
+    <row r="47" spans="1:6" ht="15.75">
+      <c r="A47" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="3" customFormat="1"/>
+    <row r="49" spans="1:6" ht="24">
+      <c r="A49" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30.75">
+      <c r="A50" s="26"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="26"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="3" customFormat="1"/>
+    <row r="53" spans="1:6" ht="36">
+      <c r="A53" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="36">
+      <c r="A54" s="25"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="25"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="25"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="25"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="25"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F58" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="24">
+      <c r="A59" s="25"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="30.75">
+      <c r="A60" s="26"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="30.75">
+      <c r="A61" s="26"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="36">
+      <c r="A62" s="26"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="45.75">
+      <c r="A63" s="26"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="30.75">
+      <c r="A64" s="26"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="48">
+      <c r="A65" s="26"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="36">
+      <c r="A66" s="26"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="26"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="26"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="30.75">
+      <c r="A69" s="26"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" s="3" customFormat="1" ht="21">
+      <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
+      <c r="C70" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="26"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="26"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="26"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="26"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="26"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" s="3" customFormat="1" ht="21">
+      <c r="A77" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="26"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="26"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="26"/>
+      <c r="B81" s="26"/>
+      <c r="C81" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="26"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="26"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="26"/>
+      <c r="B84" s="26"/>
+      <c r="C84" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="26"/>
+      <c r="B85" s="26"/>
+      <c r="C85" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="26"/>
+      <c r="B86" s="26"/>
+      <c r="C86" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="26"/>
+      <c r="B87" s="26"/>
+      <c r="C87" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="26"/>
+      <c r="B88" s="26"/>
+      <c r="C88" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="26"/>
+      <c r="B89" s="26"/>
+      <c r="C89" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="26"/>
+      <c r="B90" s="26"/>
+      <c r="C90" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="26"/>
+      <c r="B91" s="26"/>
+      <c r="C91" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="26"/>
+      <c r="B92" s="26"/>
+      <c r="C92" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="26"/>
+      <c r="B93" s="26"/>
+      <c r="C93" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="26"/>
+      <c r="B94" s="26"/>
+      <c r="C94" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="26"/>
+      <c r="B95" s="26"/>
+      <c r="C95" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="26"/>
+      <c r="B96" s="26"/>
+      <c r="C96" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" s="3" customFormat="1" ht="21">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="7"/>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="25"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="6"/>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="25"/>
+      <c r="B99" s="26"/>
+      <c r="C99" s="6"/>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="25"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="6"/>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="25"/>
+      <c r="B101" s="26"/>
+      <c r="C101" s="6"/>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="25"/>
+      <c r="B102" s="26"/>
+      <c r="C102" s="6"/>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="25"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="6"/>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="25"/>
+      <c r="B104" s="26"/>
+      <c r="C104" s="6"/>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="25"/>
+      <c r="B105" s="26"/>
+      <c r="C105" s="6"/>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="25"/>
+      <c r="B106" s="26"/>
+      <c r="C106" s="6"/>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="25"/>
+      <c r="B107" s="26"/>
+      <c r="C107" s="6"/>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="25"/>
+      <c r="B108" s="26"/>
+      <c r="C108" s="6"/>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="25"/>
+      <c r="B109" s="26"/>
+      <c r="C109" s="6"/>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="25"/>
+      <c r="B110" s="26"/>
+      <c r="C110" s="6"/>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="25"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="6"/>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="25"/>
+      <c r="B112" s="26"/>
+      <c r="C112" s="6"/>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="25"/>
+      <c r="B113" s="26"/>
+      <c r="C113" s="6"/>
+    </row>
+    <row r="114" spans="1:7" s="3" customFormat="1" ht="21">
+      <c r="A114" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B115" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="26"/>
+      <c r="B116" s="26"/>
+      <c r="C116" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="26"/>
+      <c r="B117" s="26"/>
+      <c r="C117" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="26"/>
+      <c r="B118" s="26"/>
+      <c r="C118" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="26"/>
+      <c r="B119" s="26"/>
+      <c r="C119" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="26"/>
+      <c r="B120" s="26"/>
+      <c r="C120" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="26"/>
+      <c r="B121" s="26"/>
+      <c r="C121" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="26"/>
+      <c r="B122" s="26"/>
+      <c r="C122" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="26"/>
+      <c r="B123" s="26"/>
+      <c r="C123" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="26"/>
+      <c r="B124" s="26"/>
+      <c r="C124" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="26"/>
+      <c r="B125" s="26"/>
+      <c r="C125" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" s="7" customFormat="1" ht="21">
+      <c r="A126" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="15" customHeight="1">
+      <c r="A127" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B127" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="C127" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="F127" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="15" customHeight="1">
+      <c r="A128" s="25"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="F128" s="23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="15" customHeight="1">
+      <c r="A129" s="25"/>
+      <c r="B129" s="26"/>
+      <c r="C129" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="F129" s="23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="15" customHeight="1">
+      <c r="A130" s="25"/>
+      <c r="B130" s="26"/>
+      <c r="C130" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="F130" s="23" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="15" customHeight="1">
+      <c r="A131" s="25"/>
+      <c r="B131" s="26"/>
+      <c r="C131" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="F131" s="23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="15" customHeight="1">
+      <c r="A132" s="25"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="F132" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="15" customHeight="1">
+      <c r="A133" s="25"/>
+      <c r="B133" s="26"/>
+      <c r="C133" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="F133" s="23" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" s="25"/>
+      <c r="B134" s="26"/>
+      <c r="C134" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="F134" s="23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="25"/>
+      <c r="B135" s="26"/>
+      <c r="C135" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="F135" s="23" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" s="25"/>
+      <c r="B136" s="26"/>
+      <c r="C136" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="F136" s="23" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" s="25"/>
+      <c r="B137" s="26"/>
+      <c r="C137" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="F137" s="23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" s="25"/>
+      <c r="B138" s="26"/>
+      <c r="C138" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="F138" s="23" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" s="25"/>
+      <c r="B139" s="26"/>
+      <c r="C139" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="F139" s="23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" s="25"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="F140" s="23" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" s="25"/>
+      <c r="B141" s="26"/>
+      <c r="C141" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="F141" s="23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="25"/>
+      <c r="B142" s="26"/>
+      <c r="C142" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="F142" s="23" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" s="25"/>
+      <c r="B143" s="26"/>
+      <c r="C143" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="F143" s="23" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" s="7" customFormat="1" ht="21">
+      <c r="A144" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="28.5">
+      <c r="A145" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="B145" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F145" s="24" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="28.5">
+      <c r="A146" s="26"/>
+      <c r="B146" s="26"/>
+      <c r="C146" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F146" s="24" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="28.5">
+      <c r="A147" s="26"/>
+      <c r="B147" s="26"/>
+      <c r="C147" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F147" s="24" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" s="8" customFormat="1" ht="21">
+      <c r="A148" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="B149" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F149" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="30.75">
+      <c r="A150" s="25"/>
+      <c r="B150" s="26"/>
+      <c r="C150" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F150" s="11" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="30.75">
+      <c r="A151" s="25"/>
+      <c r="B151" s="26"/>
+      <c r="C151" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F151" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="25"/>
+      <c r="B152" s="26"/>
+      <c r="C152" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F152" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="45.75">
+      <c r="A153" s="25"/>
+      <c r="B153" s="26"/>
+      <c r="C153" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F153" s="11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="25"/>
+      <c r="B154" s="26"/>
+      <c r="C154" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F154" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="30.75">
+      <c r="A155" s="25"/>
+      <c r="B155" s="26"/>
+      <c r="C155" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F155" s="11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="60.75">
+      <c r="A156" s="25"/>
+      <c r="B156" s="26"/>
+      <c r="C156" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F156" s="11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="25"/>
+      <c r="B157" s="26"/>
+      <c r="C157" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F157" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="25"/>
+      <c r="B158" s="26"/>
+      <c r="C158" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F158" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="30.75">
+      <c r="A159" s="25"/>
+      <c r="B159" s="26"/>
+      <c r="C159" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="F159" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="30.75">
+      <c r="A160" s="25"/>
+      <c r="B160" s="26"/>
+      <c r="C160" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="F160" s="11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="45.75">
+      <c r="A161" s="26"/>
+      <c r="B161" s="26"/>
+      <c r="C161" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="F161" s="11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="26"/>
+      <c r="B162" s="26"/>
+      <c r="C162" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="F162" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" s="26"/>
+      <c r="B163" s="26"/>
+      <c r="C163" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F163" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" s="26"/>
+      <c r="B164" s="26"/>
+      <c r="C164" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F164" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" s="3" customFormat="1"/>
   </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A149:A164"/>
+    <mergeCell ref="B149:B164"/>
+    <mergeCell ref="B98:B113"/>
+    <mergeCell ref="A98:A113"/>
+    <mergeCell ref="B115:B125"/>
+    <mergeCell ref="A115:A125"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B127:B143"/>
+    <mergeCell ref="A127:A143"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="B2:B12"/>
+    <mergeCell ref="B14:B30"/>
+    <mergeCell ref="A14:A30"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="B32:B45"/>
+    <mergeCell ref="A32:A45"/>
+    <mergeCell ref="A53:A69"/>
+    <mergeCell ref="B53:B69"/>
+    <mergeCell ref="B78:B96"/>
+    <mergeCell ref="A78:A96"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="A71:A76"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>